--- a/public/downloads/CamposEfficient2021.xlsx
+++ b/public/downloads/CamposEfficient2021.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>C3H6O3</t>
@@ -659,10 +682,10 @@
         <v>66</v>
       </c>
       <c r="N3" s="5">
-        <v>348.0719163417816</v>
+        <v>348071.9163417816</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03220204610433727</v>
+        <v>32.20204610433727</v>
       </c>
       <c r="P3" s="5">
         <v>10809</v>
@@ -709,10 +732,10 @@
         <v>66</v>
       </c>
       <c r="N4" s="5">
-        <v>923.908465385437</v>
+        <v>923908.465385437</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06553936762328418</v>
+        <v>65.53936762328418</v>
       </c>
       <c r="P4" s="5">
         <v>14097</v>
@@ -759,10 +782,10 @@
         <v>66</v>
       </c>
       <c r="N5" s="5">
-        <v>1319.72345995903</v>
+        <v>1319723.45995903</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1716601794951912</v>
+        <v>171.6601794951912</v>
       </c>
       <c r="P5" s="5">
         <v>7688</v>
@@ -809,10 +832,10 @@
         <v>66</v>
       </c>
       <c r="N6" s="5">
-        <v>963.7542307376862</v>
+        <v>963754.2307376862</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08491226702534679</v>
+        <v>84.91226702534679</v>
       </c>
       <c r="P6" s="5">
         <v>11350</v>
@@ -859,10 +882,10 @@
         <v>66</v>
       </c>
       <c r="N7" s="5">
-        <v>1154.671994447708</v>
+        <v>1154671.994447708</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2413107616400644</v>
+        <v>241.3107616400644</v>
       </c>
       <c r="P7" s="5">
         <v>4785</v>
@@ -909,10 +932,10 @@
         <v>66</v>
       </c>
       <c r="N8" s="5">
-        <v>201.182008266449</v>
+        <v>201182.008266449</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01791628891855454</v>
+        <v>17.91628891855454</v>
       </c>
       <c r="P8" s="5">
         <v>11229</v>
@@ -959,10 +982,10 @@
         <v>66</v>
       </c>
       <c r="N9" s="5">
-        <v>535.6275136470795</v>
+        <v>535627.5136470795</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03058456653041052</v>
+        <v>30.58456653041052</v>
       </c>
       <c r="P9" s="5">
         <v>17513</v>
@@ -1009,10 +1032,10 @@
         <v>66</v>
       </c>
       <c r="N10" s="5">
-        <v>587.0572040081024</v>
+        <v>587057.2040081024</v>
       </c>
       <c r="O10" s="4">
-        <v>0.09330216211190438</v>
+        <v>93.30216211190438</v>
       </c>
       <c r="P10" s="5">
         <v>6292</v>
@@ -1059,10 +1082,10 @@
         <v>66</v>
       </c>
       <c r="N11" s="5">
-        <v>581.9099559783936</v>
+        <v>581909.9559783936</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04232995969872653</v>
+        <v>42.32995969872653</v>
       </c>
       <c r="P11" s="5">
         <v>13747</v>
@@ -1109,10 +1132,10 @@
         <v>66</v>
       </c>
       <c r="N12" s="5">
-        <v>187.8573670387268</v>
+        <v>187857.3670387268</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02217129317109959</v>
+        <v>22.17129317109959</v>
       </c>
       <c r="P12" s="5">
         <v>8473</v>
@@ -1159,10 +1182,10 @@
         <v>66</v>
       </c>
       <c r="N13" s="5">
-        <v>837.8634173870087</v>
+        <v>837863.4173870087</v>
       </c>
       <c r="O13" s="4">
-        <v>0.08398791272925107</v>
+        <v>83.98791272925108</v>
       </c>
       <c r="P13" s="5">
         <v>9976</v>
@@ -1209,10 +1232,10 @@
         <v>66</v>
       </c>
       <c r="N14" s="5">
-        <v>1492.378657817841</v>
+        <v>1492378.657817841</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3331202361200537</v>
+        <v>333.1202361200537</v>
       </c>
       <c r="P14" s="5">
         <v>4480</v>
@@ -1259,10 +1282,10 @@
         <v>66</v>
       </c>
       <c r="N15" s="5">
-        <v>2730.296456575394</v>
+        <v>2730296.456575394</v>
       </c>
       <c r="O15" s="4">
-        <v>0.3416714374390432</v>
+        <v>341.6714374390431</v>
       </c>
       <c r="P15" s="5">
         <v>7991</v>
@@ -1309,10 +1332,10 @@
         <v>66</v>
       </c>
       <c r="N16" s="5">
-        <v>395.194281578064</v>
+        <v>395194.281578064</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09589766599807424</v>
+        <v>95.89766599807425</v>
       </c>
       <c r="P16" s="5">
         <v>4121</v>
@@ -1359,10 +1382,10 @@
         <v>66</v>
       </c>
       <c r="N17" s="5">
-        <v>1041.737653493881</v>
+        <v>1041737.653493881</v>
       </c>
       <c r="O17" s="4">
-        <v>0.0960126869579614</v>
+        <v>96.01268695796141</v>
       </c>
       <c r="P17" s="5">
         <v>10850</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,34 +1497,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7525771921679492</v>
+        <v>0.5883660431523663</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7749162016089509</v>
+        <v>0.6307040658354655</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7755036164793984</v>
+        <v>0.3714608472015739</v>
       </c>
       <c r="E3" s="4">
-        <v>88.09996220710499</v>
+        <v>83.88038548752826</v>
       </c>
       <c r="F3" s="4">
-        <v>88.87583892617346</v>
+        <v>75.77460850111878</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1501,34 +1556,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6307040658354655</v>
+      </c>
+      <c r="O3" s="5">
+        <v>18</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2444090072841302</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2311474322767562</v>
+      </c>
+      <c r="R3" s="5">
+        <v>18</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.716602459616678</v>
+        <v>0.6732031701475929</v>
       </c>
       <c r="C4" s="4">
-        <v>0.716602459616678</v>
+        <v>0.6157570880859583</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7104748140973195</v>
+        <v>0.5218180758990604</v>
       </c>
       <c r="E4" s="4">
-        <v>89.28004535147392</v>
+        <v>85.60374149659866</v>
       </c>
       <c r="F4" s="4">
-        <v>91.99711036539895</v>
+        <v>77.76845637583975</v>
       </c>
       <c r="G4" s="5">
         <v>24</v>
       </c>
       <c r="H4" s="5">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1542,25 +1615,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.6157570880859583</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1554551798213622</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1208232467699154</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6348323135418461</v>
+        <v>0.6785023860615951</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6348323135418461</v>
+        <v>0.6785023860615951</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6177513716985068</v>
+        <v>0.5761423627320568</v>
       </c>
       <c r="E5" s="4">
-        <v>90.20975056689343</v>
+        <v>83.23129251700679</v>
       </c>
       <c r="F5" s="4">
-        <v>93.0294556301268</v>
+        <v>79.26174496644289</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -1583,9 +1674,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.6785023860615951</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.08683745144212669</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08683745144212669</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,116 +1797,166 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6441463180609897</v>
+        <v>1.307845288413088</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7791514087695353</v>
+        <v>1.142504763342738</v>
       </c>
       <c r="D3" s="4">
-        <v>0.9070886874395142</v>
+        <v>1.81608694185547</v>
       </c>
       <c r="E3" s="4">
-        <v>78.80668934240309</v>
+        <v>77.10884353741537</v>
       </c>
       <c r="F3" s="4">
-        <v>67.85359184688012</v>
+        <v>66.85620183942265</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.217490297211922</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5254163414280869</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5258271657784097</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4675231105136266</v>
+        <v>1.024042965775343</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7288330286288645</v>
+        <v>1.831283468704839</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6441617262225462</v>
+        <v>1.562997303213291</v>
       </c>
       <c r="E4" s="4">
-        <v>81.09693877551024</v>
+        <v>75.46060090702936</v>
       </c>
       <c r="F4" s="4">
-        <v>69.70451155853743</v>
+        <v>60.23163683818019</v>
       </c>
       <c r="G4" s="5">
         <v>24</v>
       </c>
       <c r="H4" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.024042965775343</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.831283468704839</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3104842631534955</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3686621452421217</v>
-      </c>
+        <v>1.161766681385096</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.4497699865218223</v>
+        <v>1.745084438037928</v>
       </c>
       <c r="E5" s="4">
-        <v>79.17233560090703</v>
+        <v>67.32426303854822</v>
       </c>
       <c r="F5" s="4">
-        <v>73.54772557792725</v>
+        <v>55.36912751677822</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -1796,9 +1970,23 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.161766681385096</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +1997,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2005,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2016,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2058,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,34 +2089,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.499035545340448</v>
+        <v>0.7525771921679492</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5110767600131301</v>
+        <v>0.7749162016089509</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5373288098293744</v>
+        <v>0.7755036164793984</v>
       </c>
       <c r="E3" s="4">
-        <v>83.35789871504161</v>
+        <v>88.09996220710499</v>
       </c>
       <c r="F3" s="4">
-        <v>84.05077056922612</v>
+        <v>88.87583892617346</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1927,25 +2148,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.7749162016089509</v>
+      </c>
+      <c r="O3" s="5">
+        <v>33</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1467145273566605</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1356823831807187</v>
+      </c>
+      <c r="R3" s="5">
+        <v>33</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3830298203285659</v>
+        <v>0.716602459616678</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3830298203285659</v>
+        <v>0.716602459616678</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4027580835477635</v>
+        <v>0.7104748140973195</v>
       </c>
       <c r="E4" s="4">
-        <v>84.62159863945577</v>
+        <v>89.28004535147392</v>
       </c>
       <c r="F4" s="4">
-        <v>87.08379940343019</v>
+        <v>91.99711036539895</v>
       </c>
       <c r="G4" s="5">
         <v>24</v>
@@ -1968,25 +2207,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.716602459616678</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1150730924023611</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1150730924023611</v>
+      </c>
+      <c r="R4" s="5">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2301363023559707</v>
+        <v>0.6348323135418461</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2301363023559707</v>
+        <v>0.6348323135418461</v>
       </c>
       <c r="D5" s="4">
-        <v>0.266503082954929</v>
+        <v>0.6177513716985068</v>
       </c>
       <c r="E5" s="4">
-        <v>81.2755102040816</v>
+        <v>90.20975056689343</v>
       </c>
       <c r="F5" s="4">
-        <v>84.51715137956749</v>
+        <v>93.0294556301268</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -2009,9 +2266,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.6348323135418461</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09607579001284587</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09607579001284587</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2297,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2305,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2316,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2358,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,34 +2389,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2412144203763829</v>
+        <v>0.6441463180609897</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2534930395507815</v>
+        <v>0.7791514087695353</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2176142132533093</v>
+        <v>0.9070886874395142</v>
       </c>
       <c r="E3" s="4">
-        <v>83.54024943310648</v>
+        <v>78.80668934240309</v>
       </c>
       <c r="F3" s="4">
-        <v>77.28405418841594</v>
+        <v>67.85359184688012</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2140,34 +2448,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.7298618811484451</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4563760173526507</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.334384874653123</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3592333909909128</v>
+        <v>0.4675231105136266</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3487360087257528</v>
+        <v>0.7288330286288645</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3353881952206492</v>
+        <v>0.6441617262225462</v>
       </c>
       <c r="E4" s="4">
-        <v>87.04081632653069</v>
+        <v>81.09693877551024</v>
       </c>
       <c r="F4" s="4">
-        <v>83.84740865026266</v>
+        <v>69.70451155853743</v>
       </c>
       <c r="G4" s="5">
         <v>24</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2181,34 +2507,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.5762167508563127</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3994367659305875</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4407246532007081</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3844725357372998</v>
+        <v>0.3104842631534955</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3844725357372998</v>
+        <v>0.3686621452421217</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4093259242057243</v>
+        <v>0.4497699865218223</v>
       </c>
       <c r="E5" s="4">
-        <v>88.86054421768708</v>
+        <v>79.17233560090703</v>
       </c>
       <c r="F5" s="4">
-        <v>87.91387024608504</v>
+        <v>73.54772557792725</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
       </c>
       <c r="H5" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2222,9 +2566,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3104842631534955</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3686621452421217</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2595,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2603,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2614,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2656,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,34 +2687,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9656995970978488</v>
+        <v>0.499035545340448</v>
       </c>
       <c r="C3" s="4">
-        <v>1.020251345523038</v>
+        <v>0.5110767600131301</v>
       </c>
       <c r="D3" s="4">
-        <v>0.9857525235057509</v>
+        <v>0.5373288098293744</v>
       </c>
       <c r="E3" s="4">
-        <v>89.38964474678765</v>
+        <v>83.35789871504161</v>
       </c>
       <c r="F3" s="4">
-        <v>86.25776783494801</v>
+        <v>84.05077056922612</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I3" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2353,25 +2746,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.4965184714242616</v>
+      </c>
+      <c r="O3" s="5">
+        <v>32</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2687596040669464</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2460325452834126</v>
+      </c>
+      <c r="R3" s="5">
+        <v>32</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.0583109513479</v>
+        <v>0.3830298203285659</v>
       </c>
       <c r="C4" s="4">
-        <v>1.0583109513479</v>
+        <v>0.3830298203285659</v>
       </c>
       <c r="D4" s="4">
-        <v>1.037434713846186</v>
+        <v>0.4027580835477635</v>
       </c>
       <c r="E4" s="4">
-        <v>97.8486394557823</v>
+        <v>84.62159863945577</v>
       </c>
       <c r="F4" s="4">
-        <v>96.94770693512262</v>
+        <v>87.08379940343019</v>
       </c>
       <c r="G4" s="5">
         <v>24</v>
@@ -2394,25 +2805,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3830298203285659</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2285577835785348</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2285577835785348</v>
+      </c>
+      <c r="R4" s="5">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9382786734027265</v>
+        <v>0.2301363023559707</v>
       </c>
       <c r="C5" s="4">
-        <v>0.9382786734027265</v>
+        <v>0.2301363023559707</v>
       </c>
       <c r="D5" s="4">
-        <v>0.9118307067078</v>
+        <v>0.266503082954929</v>
       </c>
       <c r="E5" s="4">
-        <v>98.63945578231292</v>
+        <v>81.2755102040816</v>
       </c>
       <c r="F5" s="4">
-        <v>98.51789709172259</v>
+        <v>84.51715137956749</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -2435,9 +2864,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1998446715991259</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2319382410156297</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2319382410156297</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2895,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2903,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2914,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2956,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,34 +2987,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9658693135805897</v>
+        <v>0.2412144203763829</v>
       </c>
       <c r="C3" s="4">
-        <v>0.9392368321504923</v>
+        <v>0.2534930395507815</v>
       </c>
       <c r="D3" s="4">
-        <v>0.9125869533447096</v>
+        <v>0.2176142132533093</v>
       </c>
       <c r="E3" s="4">
-        <v>84.1080876795164</v>
+        <v>83.54024943310648</v>
       </c>
       <c r="F3" s="4">
-        <v>84.4525229927891</v>
+        <v>77.28405418841594</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I3" s="5">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2566,34 +3046,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1817746219318139</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2121743004378666</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.169687995517908</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.097036609495142</v>
+        <v>0.3592333909909128</v>
       </c>
       <c r="C4" s="4">
-        <v>1.097036609495142</v>
+        <v>0.3487360087257528</v>
       </c>
       <c r="D4" s="4">
-        <v>1.089103935355431</v>
+        <v>0.3353881952206492</v>
       </c>
       <c r="E4" s="4">
-        <v>88.35884353741496</v>
+        <v>87.04081632653069</v>
       </c>
       <c r="F4" s="4">
-        <v>89.8545861297539</v>
+        <v>83.84740865026266</v>
       </c>
       <c r="G4" s="5">
         <v>24</v>
       </c>
       <c r="H4" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2607,25 +3105,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.33202550602906</v>
+      </c>
+      <c r="O4" s="5">
+        <v>23</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1504945068359236</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1453574124783319</v>
+      </c>
+      <c r="R4" s="5">
+        <v>23</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.221701340564062</v>
+        <v>0.3844725357372998</v>
       </c>
       <c r="C5" s="4">
-        <v>1.221701340564062</v>
+        <v>0.3844725357372998</v>
       </c>
       <c r="D5" s="4">
-        <v>1.20862083304723</v>
+        <v>0.4093259242057243</v>
       </c>
       <c r="E5" s="4">
-        <v>87.43197278911566</v>
+        <v>88.86054421768708</v>
       </c>
       <c r="F5" s="4">
-        <v>89.64578672632372</v>
+        <v>87.91387024608504</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -2648,9 +3164,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3844725357372998</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1198468323071159</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1198468323071159</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3195,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3203,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3214,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3256,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,34 +3287,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9979786166522886</v>
+        <v>0.9656995970978488</v>
       </c>
       <c r="C3" s="4">
-        <v>1.040493664113267</v>
+        <v>1.020251345523038</v>
       </c>
       <c r="D3" s="4">
-        <v>1.013827026450697</v>
+        <v>0.9857525235057509</v>
       </c>
       <c r="E3" s="4">
-        <v>91.55895691609943</v>
+        <v>89.38964474678765</v>
       </c>
       <c r="F3" s="4">
-        <v>88.50391498881378</v>
+        <v>86.25776783494801</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2779,25 +3346,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>1.020251345523038</v>
+      </c>
+      <c r="O3" s="5">
+        <v>26</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1138990537705885</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08217319201670754</v>
+      </c>
+      <c r="R3" s="5">
+        <v>26</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.095100179866716</v>
+        <v>1.0583109513479</v>
       </c>
       <c r="C4" s="4">
-        <v>1.095100179866716</v>
+        <v>1.0583109513479</v>
       </c>
       <c r="D4" s="4">
-        <v>1.076475875383376</v>
+        <v>1.037434713846186</v>
       </c>
       <c r="E4" s="4">
-        <v>98.26105442176872</v>
+        <v>97.8486394557823</v>
       </c>
       <c r="F4" s="4">
-        <v>97.2268829231915</v>
+        <v>96.94770693512262</v>
       </c>
       <c r="G4" s="5">
         <v>24</v>
@@ -2820,34 +3405,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>1.0583109513479</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09743454500009709</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09743454500009709</v>
+      </c>
+      <c r="R4" s="5">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9641315473241304</v>
+        <v>0.9382786734027265</v>
       </c>
       <c r="C5" s="4">
-        <v>0.9939711803557941</v>
+        <v>0.9382786734027265</v>
       </c>
       <c r="D5" s="4">
-        <v>0.947470827214134</v>
+        <v>0.9118307067078</v>
       </c>
       <c r="E5" s="4">
-        <v>96.73469387755095</v>
+        <v>98.63945578231292</v>
       </c>
       <c r="F5" s="4">
-        <v>94.44071588366869</v>
+        <v>98.51789709172259</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2861,9 +3464,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.9382786734027265</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07308147960326827</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07308147960326827</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3495,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3503,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3514,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3556,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,34 +3587,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6336592250191919</v>
+        <v>0.9658693135805897</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6766366625343452</v>
+        <v>0.9392368321504923</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7438341913095498</v>
+        <v>0.9125869533447096</v>
       </c>
       <c r="E3" s="4">
-        <v>78.87093726379473</v>
+        <v>84.1080876795164</v>
       </c>
       <c r="F3" s="4">
-        <v>75.15722097936822</v>
+        <v>84.4525229927891</v>
       </c>
       <c r="G3" s="5">
         <v>36</v>
       </c>
       <c r="H3" s="5">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I3" s="5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2992,37 +3646,55 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.9392368321504923</v>
+      </c>
+      <c r="O3" s="5">
+        <v>30</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1991922952112986</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1855450753338333</v>
+      </c>
+      <c r="R3" s="5">
+        <v>30</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8072122834099572</v>
+        <v>1.097036609495142</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6575939692771038</v>
+        <v>1.097036609495142</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8636906620833044</v>
+        <v>1.089103935355431</v>
       </c>
       <c r="E4" s="4">
-        <v>86.78996598639452</v>
+        <v>88.35884353741496</v>
       </c>
       <c r="F4" s="4">
-        <v>83.58594332587761</v>
+        <v>89.8545861297539</v>
       </c>
       <c r="G4" s="5">
         <v>24</v>
       </c>
       <c r="H4" s="5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -3031,39 +3703,57 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-1.097036609495142</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1812554124230725</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1812554124230725</v>
+      </c>
+      <c r="R4" s="5">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.744906215775463</v>
+        <v>1.221701340564062</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4910118683317506</v>
+        <v>1.221701340564062</v>
       </c>
       <c r="D5" s="4">
-        <v>0.8188470293169511</v>
+        <v>1.20862083304723</v>
       </c>
       <c r="E5" s="4">
-        <v>89.76757369614513</v>
+        <v>87.43197278911566</v>
       </c>
       <c r="F5" s="4">
-        <v>90.8296047725576</v>
+        <v>89.64578672632372</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -3072,11 +3762,29 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-1.221701340564062</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1167090999078511</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1167090999078511</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3795,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.9979786166522886</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.040493664113267</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.013827026450697</v>
+      </c>
+      <c r="E3" s="4">
+        <v>91.55895691609943</v>
+      </c>
+      <c r="F3" s="4">
+        <v>88.50391498881378</v>
+      </c>
+      <c r="G3" s="5">
+        <v>36</v>
+      </c>
+      <c r="H3" s="5">
+        <v>27</v>
+      </c>
+      <c r="I3" s="5">
+        <v>9</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.040493664113267</v>
+      </c>
+      <c r="O3" s="5">
+        <v>27</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1092716544407738</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08900880930639393</v>
+      </c>
+      <c r="R3" s="5">
+        <v>27</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.095100179866716</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.095100179866716</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.076475875383376</v>
+      </c>
+      <c r="E4" s="4">
+        <v>98.26105442176872</v>
+      </c>
+      <c r="F4" s="4">
+        <v>97.2268829231915</v>
+      </c>
+      <c r="G4" s="5">
+        <v>24</v>
+      </c>
+      <c r="H4" s="5">
+        <v>24</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.095100179866716</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09079190135033184</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09079190135033184</v>
+      </c>
+      <c r="R4" s="5">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.9641315473241304</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.9939711803557941</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.947470827214134</v>
+      </c>
+      <c r="E5" s="4">
+        <v>96.73469387755095</v>
+      </c>
+      <c r="F5" s="4">
+        <v>94.44071588366869</v>
+      </c>
+      <c r="G5" s="5">
+        <v>6</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.9939711803557941</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.08658023229129153</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06808871911155337</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6336592250191919</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6766366625343452</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.7438341913095498</v>
+      </c>
+      <c r="E3" s="4">
+        <v>78.87093726379473</v>
+      </c>
+      <c r="F3" s="4">
+        <v>75.15722097936822</v>
+      </c>
+      <c r="G3" s="5">
+        <v>36</v>
+      </c>
+      <c r="H3" s="5">
+        <v>22</v>
+      </c>
+      <c r="I3" s="5">
+        <v>14</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.5990297479125085</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4542793568951208</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4092469488561549</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.8072122834099572</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.6575939692771038</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.8636906620833044</v>
+      </c>
+      <c r="E4" s="4">
+        <v>86.78996598639452</v>
+      </c>
+      <c r="F4" s="4">
+        <v>83.58594332587761</v>
+      </c>
+      <c r="G4" s="5">
+        <v>24</v>
+      </c>
+      <c r="H4" s="5">
+        <v>19</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.6933360833106427</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.470801482762409</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4687780346605542</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.744906215775463</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4910118683317506</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.8188470293169511</v>
+      </c>
+      <c r="E5" s="4">
+        <v>89.76757369614513</v>
+      </c>
+      <c r="F5" s="4">
+        <v>90.8296047725576</v>
+      </c>
+      <c r="G5" s="5">
+        <v>6</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.6773197783151422</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5540031028796619</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5540031028796619</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>69.6969696969697</v>
+      </c>
+      <c r="C3" s="3">
+        <v>30.3030303030303</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.2475151612608029</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2117071019252557</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.2434514611881286</v>
+      </c>
+      <c r="K3" s="4">
+        <v>86.32962275819416</v>
+      </c>
+      <c r="L3" s="4">
+        <v>80.22574740695622</v>
+      </c>
+      <c r="M3" s="5">
+        <v>66</v>
+      </c>
+      <c r="N3" s="5">
+        <v>348071.9163417816</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.20204610433727</v>
+      </c>
+      <c r="P3" s="5">
+        <v>10809</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>51.51515151515152</v>
+      </c>
+      <c r="C4" s="3">
+        <v>48.48484848484848</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.4642177154601919</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.4486043469751284</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.5223456317768291</v>
+      </c>
+      <c r="K4" s="4">
+        <v>78.16944959802096</v>
+      </c>
+      <c r="L4" s="4">
+        <v>72.96590061690807</v>
+      </c>
+      <c r="M4" s="5">
+        <v>66</v>
+      </c>
+      <c r="N4" s="5">
+        <v>923908.465385437</v>
+      </c>
+      <c r="O4" s="4">
+        <v>65.53936762328418</v>
+      </c>
+      <c r="P4" s="5">
+        <v>14097</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>92.42424242424242</v>
+      </c>
+      <c r="C5" s="3">
+        <v>7.575757575757576</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2848073801814382</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2486625855057841</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2446644643983809</v>
+      </c>
+      <c r="K5" s="4">
+        <v>88.21377035662745</v>
+      </c>
+      <c r="L5" s="4">
+        <v>87.70896888346638</v>
+      </c>
+      <c r="M5" s="5">
+        <v>66</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1319723.45995903</v>
+      </c>
+      <c r="O5" s="4">
+        <v>171.6601794951912</v>
+      </c>
+      <c r="P5" s="5">
+        <v>7688</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>59.09090909090909</v>
+      </c>
+      <c r="C6" s="3">
+        <v>39.39393939393939</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1.515151515151515</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.515151515151515</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.3270353509219522</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3299628352174999</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.4187705417114689</v>
+      </c>
+      <c r="K6" s="4">
+        <v>82.27891156462583</v>
+      </c>
+      <c r="L6" s="4">
+        <v>76.98223849230486</v>
+      </c>
+      <c r="M6" s="5">
+        <v>66</v>
+      </c>
+      <c r="N6" s="5">
+        <v>963754.2307376862</v>
+      </c>
+      <c r="O6" s="4">
+        <v>84.91226702534679</v>
+      </c>
+      <c r="P6" s="5">
+        <v>11350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1375142155559574</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1375142155559574</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1372896298530359</v>
+      </c>
+      <c r="K7" s="4">
+        <v>93.04988662131518</v>
+      </c>
+      <c r="L7" s="4">
+        <v>94.27293064876952</v>
+      </c>
+      <c r="M7" s="5">
+        <v>66</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1154671.994447708</v>
+      </c>
+      <c r="O7" s="4">
+        <v>241.3107616400644</v>
+      </c>
+      <c r="P7" s="5">
+        <v>4785</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>62.12121212121212</v>
+      </c>
+      <c r="C8" s="3">
+        <v>37.87878787878788</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1977374740393052</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1642847240176325</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.262336193745653</v>
+      </c>
+      <c r="K8" s="4">
+        <v>84.44805194805184</v>
+      </c>
+      <c r="L8" s="4">
+        <v>76.81665649786426</v>
+      </c>
+      <c r="M8" s="5">
+        <v>66</v>
+      </c>
+      <c r="N8" s="5">
+        <v>201182.008266449</v>
+      </c>
+      <c r="O8" s="4">
+        <v>17.91628891855454</v>
+      </c>
+      <c r="P8" s="5">
+        <v>11229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="C9" s="3">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.515151515151515</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.7645851448231811</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.7869184263636957</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1.146657920072276</v>
+      </c>
+      <c r="K9" s="4">
+        <v>75.61997526283245</v>
+      </c>
+      <c r="L9" s="4">
+        <v>63.40298962782175</v>
+      </c>
+      <c r="M9" s="5">
+        <v>66</v>
+      </c>
+      <c r="N9" s="5">
+        <v>535627.5136470795</v>
+      </c>
+      <c r="O9" s="4">
+        <v>30.58456653041052</v>
+      </c>
+      <c r="P9" s="5">
+        <v>17513</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>95.45454545454545</v>
+      </c>
+      <c r="C10" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1306050294329321</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1240591682967851</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1334754537067264</v>
+      </c>
+      <c r="K10" s="4">
+        <v>88.72088229231075</v>
+      </c>
+      <c r="L10" s="4">
+        <v>90.38844824079756</v>
+      </c>
+      <c r="M10" s="5">
+        <v>66</v>
+      </c>
+      <c r="N10" s="5">
+        <v>587057.2040081024</v>
+      </c>
+      <c r="O10" s="4">
+        <v>93.30216211190438</v>
+      </c>
+      <c r="P10" s="5">
+        <v>6292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>31.81818181818182</v>
+      </c>
+      <c r="C11" s="3">
+        <v>68.18181818181817</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.4224079482719772</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.37979201942206</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.3659610833482541</v>
+      </c>
+      <c r="K11" s="4">
+        <v>79.67274788703332</v>
+      </c>
+      <c r="L11" s="4">
+        <v>69.04430208121379</v>
+      </c>
+      <c r="M11" s="5">
+        <v>66</v>
+      </c>
+      <c r="N11" s="5">
+        <v>581909.9559783936</v>
+      </c>
+      <c r="O11" s="4">
+        <v>42.32995969872653</v>
+      </c>
+      <c r="P11" s="5">
+        <v>13747</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>93.93939393939394</v>
+      </c>
+      <c r="C12" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2507933636119498</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2379041564685132</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2368620613896876</v>
+      </c>
+      <c r="K12" s="4">
+        <v>83.62811791383217</v>
+      </c>
+      <c r="L12" s="4">
+        <v>85.19608840078664</v>
+      </c>
+      <c r="M12" s="5">
+        <v>66</v>
+      </c>
+      <c r="N12" s="5">
+        <v>187857.3670387268</v>
+      </c>
+      <c r="O12" s="4">
+        <v>22.17129317109959</v>
+      </c>
+      <c r="P12" s="5">
+        <v>8473</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="C13" s="3">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.18135187838891</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1528517133772216</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1742287755728625</v>
+      </c>
+      <c r="K13" s="4">
+        <v>85.29684601113155</v>
+      </c>
+      <c r="L13" s="4">
+        <v>80.63707545251226</v>
+      </c>
+      <c r="M13" s="5">
+        <v>66</v>
+      </c>
+      <c r="N13" s="5">
+        <v>837863.4173870087</v>
+      </c>
+      <c r="O13" s="4">
+        <v>83.98791272925108</v>
+      </c>
+      <c r="P13" s="5">
+        <v>9976</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>84.84848484848484</v>
+      </c>
+      <c r="C14" s="3">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1042012711115625</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.08773965982243458</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.09283138716668263</v>
+      </c>
+      <c r="K14" s="4">
+        <v>93.30653473510587</v>
+      </c>
+      <c r="L14" s="4">
+        <v>91.25957562199112</v>
+      </c>
+      <c r="M14" s="5">
+        <v>66</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1492378.657817841</v>
+      </c>
+      <c r="O14" s="4">
+        <v>333.1202361200537</v>
+      </c>
+      <c r="P14" s="5">
+        <v>4480</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>90.90909090909091</v>
+      </c>
+      <c r="C15" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1851713200789029</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1769456126269308</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1840920238811511</v>
+      </c>
+      <c r="K15" s="4">
+        <v>85.95598845598796</v>
+      </c>
+      <c r="L15" s="4">
+        <v>86.88902447291818</v>
+      </c>
+      <c r="M15" s="5">
+        <v>66</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2730296.456575394</v>
+      </c>
+      <c r="O15" s="4">
+        <v>341.6714374390431</v>
+      </c>
+      <c r="P15" s="5">
+        <v>7991</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>84.84848484848484</v>
+      </c>
+      <c r="C16" s="3">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1004888876670238</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.08790512641497085</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.08785127852395866</v>
+      </c>
+      <c r="K16" s="4">
+        <v>94.46660482374725</v>
+      </c>
+      <c r="L16" s="4">
+        <v>92.2156125008478</v>
+      </c>
+      <c r="M16" s="5">
+        <v>66</v>
+      </c>
+      <c r="N16" s="5">
+        <v>395194.281578064</v>
+      </c>
+      <c r="O16" s="4">
+        <v>95.89766599807425</v>
+      </c>
+      <c r="P16" s="5">
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="C17" s="3">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.4693531977545475</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.4521460871942597</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.5270339532374112</v>
+      </c>
+      <c r="K17" s="4">
+        <v>82.74118738404395</v>
+      </c>
+      <c r="L17" s="4">
+        <v>79.64697308657153</v>
+      </c>
+      <c r="M17" s="5">
+        <v>66</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1041737.653493881</v>
+      </c>
+      <c r="O17" s="4">
+        <v>96.01268695796141</v>
+      </c>
+      <c r="P17" s="5">
+        <v>10850</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3847,9 +6013,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>46</v>
+      </c>
+      <c r="C3" s="5">
+        <v>20</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>34</v>
+      </c>
+      <c r="C4" s="5">
+        <v>32</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>61</v>
+      </c>
+      <c r="C5" s="5">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>39</v>
+      </c>
+      <c r="C6" s="5">
+        <v>26</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>66</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>41</v>
+      </c>
+      <c r="C8" s="5">
+        <v>25</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5">
+        <v>48</v>
+      </c>
+      <c r="D9" s="5">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>2</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>63</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>21</v>
+      </c>
+      <c r="C11" s="5">
+        <v>45</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>62</v>
+      </c>
+      <c r="C12" s="5">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>51</v>
+      </c>
+      <c r="C13" s="5">
+        <v>15</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>56</v>
+      </c>
+      <c r="C14" s="5">
+        <v>10</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>60</v>
+      </c>
+      <c r="C15" s="5">
+        <v>6</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>56</v>
+      </c>
+      <c r="C16" s="5">
+        <v>10</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>48</v>
+      </c>
+      <c r="C17" s="5">
+        <v>18</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6781,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6823,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6854,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3352742791299142</v>
@@ -3960,10 +6913,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2365006847618542</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3112217314695822</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2704940401743303</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2176975052899106</v>
@@ -4001,10 +6972,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.182313069951443</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1861945056736452</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1735726461436639</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2498152984301806</v>
@@ -4042,9 +7031,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2498152984301806</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1105583623567578</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1105583623567578</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7062,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7081,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7123,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7154,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4793338620545712</v>
@@ -4173,10 +7213,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.261748036732109</v>
+      </c>
+      <c r="O3" s="5">
+        <v>19</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.454508610990181</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4856732270521322</v>
+      </c>
+      <c r="R3" s="5">
+        <v>19</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.5284825074820798</v>
@@ -4214,10 +7272,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1481754930891969</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4628533187687032</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3879226356282419</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5279299290462115</v>
@@ -4255,9 +7331,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5279299290462115</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4565616185416512</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7360,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7379,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7421,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7452,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4351769901775325</v>
@@ -4386,10 +7511,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2824309715401676</v>
+      </c>
+      <c r="O3" s="5">
+        <v>32</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3410802205226239</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.294852504655004</v>
+      </c>
+      <c r="R3" s="5">
+        <v>32</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2792313965941483</v>
@@ -4427,10 +7570,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.178446861844663</v>
+      </c>
+      <c r="O4" s="5">
+        <v>23</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.235957452482749</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2120746640573141</v>
+      </c>
+      <c r="R4" s="5">
+        <v>23</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1664270731430998</v>
@@ -4468,9 +7629,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.08336501773402698</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1425700489290804</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1425700489290804</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7660,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7679,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7721,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7752,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4416354538864495</v>
@@ -4599,10 +7811,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1668170803688245</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3664842893871482</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4330698539663239</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3416980512739969</v>
@@ -4640,10 +7870,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.270213575956892</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3169011667964461</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3114921601638262</v>
+      </c>
+      <c r="R4" s="5">
+        <v>19</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1434398356542938</v>
@@ -4681,9 +7929,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1283523900644553</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1308784566327996</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09083034417498766</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7960,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7979,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8021,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8052,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.891114195748157</v>
@@ -4812,10 +8111,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.891114195748157</v>
+      </c>
+      <c r="O3" s="5">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1550477370616376</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1550477370616376</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.8438621777351821</v>
@@ -4853,10 +8170,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.8438621777351821</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1274478361816526</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1274478361816526</v>
+      </c>
+      <c r="R4" s="5">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.7954851719856819</v>
@@ -4894,9 +8229,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.7954851719856819</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07257860401909492</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07257860401909492</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8260,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5883660431523663</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.6307040658354655</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.3714608472015739</v>
-      </c>
-      <c r="E3" s="4">
-        <v>83.88038548752826</v>
-      </c>
-      <c r="F3" s="4">
-        <v>75.77460850111878</v>
-      </c>
-      <c r="G3" s="5">
-        <v>36</v>
-      </c>
-      <c r="H3" s="5">
-        <v>18</v>
-      </c>
-      <c r="I3" s="5">
-        <v>18</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.6732031701475929</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6157570880859583</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5218180758990604</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.60374149659866</v>
-      </c>
-      <c r="F4" s="4">
-        <v>77.76845637583975</v>
-      </c>
-      <c r="G4" s="5">
-        <v>24</v>
-      </c>
-      <c r="H4" s="5">
-        <v>17</v>
-      </c>
-      <c r="I4" s="5">
-        <v>7</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6785023860615951</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6785023860615951</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5761423627320568</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.23129251700679</v>
-      </c>
-      <c r="F5" s="4">
-        <v>79.26174496644289</v>
-      </c>
-      <c r="G5" s="5">
-        <v>6</v>
-      </c>
-      <c r="H5" s="5">
-        <v>6</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.307845288413088</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.142504763342738</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.81608694185547</v>
-      </c>
-      <c r="E3" s="4">
-        <v>77.10884353741537</v>
-      </c>
-      <c r="F3" s="4">
-        <v>66.85620183942265</v>
-      </c>
-      <c r="G3" s="5">
-        <v>36</v>
-      </c>
-      <c r="H3" s="5">
-        <v>11</v>
-      </c>
-      <c r="I3" s="5">
-        <v>23</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.024042965775343</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.831283468704839</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.562997303213291</v>
-      </c>
-      <c r="E4" s="4">
-        <v>75.46060090702936</v>
-      </c>
-      <c r="F4" s="4">
-        <v>60.23163683818019</v>
-      </c>
-      <c r="G4" s="5">
-        <v>24</v>
-      </c>
-      <c r="H4" s="5">
-        <v>3</v>
-      </c>
-      <c r="I4" s="5">
-        <v>19</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.161766681385096</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.745084438037928</v>
-      </c>
-      <c r="E5" s="4">
-        <v>67.32426303854822</v>
-      </c>
-      <c r="F5" s="4">
-        <v>55.36912751677822</v>
-      </c>
-      <c r="G5" s="5">
-        <v>6</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>6</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/CamposEfficient2021.xlsx
+++ b/public/downloads/CamposEfficient2021.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6307040658354655</v>
+        <v>-0.5750536730189424</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2444090072841302</v>
+        <v>0.2400614492202976</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2311474322767562</v>
+        <v>0.2286356931287045</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6157570880859583</v>
+        <v>-0.6100725495177244</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1554551798213622</v>
+        <v>0.1564026029160678</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1208232467699154</v>
+        <v>0.1204888621482546</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.6785023860615951</v>
+        <v>-0.6598771765232527</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.08683745144212669</v>
+        <v>0.08113548378060405</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08683745144212669</v>
+        <v>0.08113548378060405</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -1857,16 +1857,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>1.217490297211922</v>
+        <v>1.248498801354993</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5254163414280869</v>
+        <v>0.5248581982693135</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5258271657784097</v>
+        <v>0.5241527363020899</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -2149,16 +2149,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7749162016089509</v>
+        <v>0.763790453194293</v>
       </c>
       <c r="O3" s="5">
         <v>33</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1467145273566605</v>
+        <v>0.1454783330883652</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1356823831807187</v>
+        <v>0.1353452392893655</v>
       </c>
       <c r="R3" s="5">
         <v>33</v>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.716602459616678</v>
+        <v>0.7177465965537024</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6348323135418461</v>
+        <v>0.6341005259614327</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -2449,16 +2449,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7298618811484451</v>
+        <v>0.7662200050781323</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4563760173526507</v>
+        <v>0.4671138811924951</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.334384874653123</v>
+        <v>0.3341220123164044</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.5762167508563127</v>
+        <v>0.7789466452948073</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3994367659305875</v>
+        <v>0.5070465406852348</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4407246532007081</v>
+        <v>0.3784618951416174</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -2747,16 +2747,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4965184714242616</v>
+        <v>0.478059438261738</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2687596040669464</v>
+        <v>0.2670722456296177</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2460325452834126</v>
+        <v>0.2452879566140756</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -2806,16 +2806,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3830298203285659</v>
+        <v>0.354124049024648</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2285577835785348</v>
+        <v>0.2257406181886884</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2285577835785348</v>
+        <v>0.2257406181886884</v>
       </c>
       <c r="R4" s="5">
         <v>24</v>
@@ -2865,16 +2865,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1998446715991259</v>
+        <v>0.09721942781007442</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2319382410156297</v>
+        <v>0.2205868964322922</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2319382410156297</v>
+        <v>0.2205868964322922</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -3047,16 +3047,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1817746219318139</v>
+        <v>-0.2003003330883502</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2121743004378666</v>
+        <v>0.2142831430950243</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.169687995517908</v>
+        <v>0.1672749583602727</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -3106,16 +3106,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.33202550602906</v>
+        <v>-0.3507671943005164</v>
       </c>
       <c r="O4" s="5">
         <v>23</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1504945068359236</v>
+        <v>0.147507924708649</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1453574124783319</v>
+        <v>0.1430558349660216</v>
       </c>
       <c r="R4" s="5">
         <v>23</v>
@@ -3165,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3844725357372998</v>
+        <v>-0.382368435017078</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -3347,16 +3347,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>1.020251345523038</v>
+        <v>1.016129306397168</v>
       </c>
       <c r="O3" s="5">
         <v>26</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1138990537705885</v>
+        <v>0.1126353133390252</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08217319201670754</v>
+        <v>0.08200879723680035</v>
       </c>
       <c r="R3" s="5">
         <v>26</v>
@@ -3406,16 +3406,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>1.0583109513479</v>
+        <v>1.047957124607812</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09743454500009709</v>
+        <v>0.09703759834076446</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09743454500009709</v>
+        <v>0.09703759834076446</v>
       </c>
       <c r="R4" s="5">
         <v>24</v>
@@ -3465,16 +3465,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.9382786734027265</v>
+        <v>0.907608683854356</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07308147960326827</v>
+        <v>0.07224906201891557</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07308147960326827</v>
+        <v>0.07224906201891557</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -3647,16 +3647,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.9392368321504923</v>
+        <v>-0.9131319366527872</v>
       </c>
       <c r="O3" s="5">
         <v>30</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1991922952112986</v>
+        <v>0.1980836585446516</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1855450753338333</v>
+        <v>0.1838210226819057</v>
       </c>
       <c r="R3" s="5">
         <v>30</v>
@@ -3706,16 +3706,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.097036609495142</v>
+        <v>-1.085616306820427</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1812554124230725</v>
+        <v>0.1804866463284368</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1812554124230725</v>
+        <v>0.1804866463284368</v>
       </c>
       <c r="R4" s="5">
         <v>24</v>
@@ -3765,7 +3765,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.221701340564062</v>
+        <v>-1.207164306990066</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -3947,16 +3947,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>1.040493664113267</v>
+        <v>1.067968168502311</v>
       </c>
       <c r="O3" s="5">
         <v>27</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1092716544407738</v>
+        <v>0.1133288284854004</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08900880930639393</v>
+        <v>0.08526020656954793</v>
       </c>
       <c r="R3" s="5">
         <v>27</v>
@@ -4006,16 +4006,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>1.095100179866716</v>
+        <v>1.083407713220467</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09079190135033184</v>
+        <v>0.09011571094300071</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09079190135033184</v>
+        <v>0.09011571094300071</v>
       </c>
       <c r="R4" s="5">
         <v>24</v>
@@ -4065,16 +4065,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.9939711803557941</v>
+        <v>0.9571059955970256</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.08658023229129153</v>
+        <v>0.07429183737170202</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06808871911155337</v>
+        <v>0.06071568215979965</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -4247,16 +4247,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5990297479125085</v>
+        <v>0.5706690258740679</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4542793568951208</v>
+        <v>0.449973472533704</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4092469488561549</v>
+        <v>0.4073574511808257</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -4306,13 +4306,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6933360833106427</v>
+        <v>0.6998784879191788</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.470801482762409</v>
+        <v>0.4697110819943197</v>
       </c>
       <c r="Q4" s="4">
         <v>0.4687780346605542</v>
@@ -4365,7 +4365,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6773197783151422</v>
+        <v>0.6392295286191754</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -4511,13 +4511,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.2475151612608029</v>
+        <v>0.2468126033422115</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2117071019252557</v>
+        <v>0.211459014263756</v>
       </c>
       <c r="J3" s="4">
-        <v>0.2434514611881286</v>
+        <v>0.2497604639343546</v>
       </c>
       <c r="K3" s="4">
         <v>86.32962275819416</v>
@@ -4561,13 +4561,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.4642177154601919</v>
+        <v>0.463718551413642</v>
       </c>
       <c r="I4" s="4">
-        <v>0.4486043469751284</v>
+        <v>0.4485946192968681</v>
       </c>
       <c r="J4" s="4">
-        <v>0.5223456317768291</v>
+        <v>0.5226022218998509</v>
       </c>
       <c r="K4" s="4">
         <v>78.16944959802096</v>
@@ -4611,13 +4611,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2848073801814382</v>
+        <v>0.283121970969189</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2486625855057841</v>
+        <v>0.2452313645031957</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2446644643983809</v>
+        <v>0.241467578563334</v>
       </c>
       <c r="K5" s="4">
         <v>88.21377035662745</v>
@@ -4661,13 +4661,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3270353509219522</v>
+        <v>0.3486846029776169</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3299628352174999</v>
+        <v>0.3256947771324109</v>
       </c>
       <c r="J6" s="4">
-        <v>0.4187705417114689</v>
+        <v>0.455615443697544</v>
       </c>
       <c r="K6" s="4">
         <v>82.27891156462583</v>
@@ -4711,13 +4711,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1375142155559574</v>
+        <v>0.1371815614500546</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1375142155559574</v>
+        <v>0.1371815614500546</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1372896298530359</v>
+        <v>0.1371184660647562</v>
       </c>
       <c r="K7" s="4">
         <v>93.04988662131518</v>
@@ -4761,13 +4761,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1977374740393052</v>
+        <v>0.1951922355242419</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1642847240176325</v>
+        <v>0.1622089276956252</v>
       </c>
       <c r="J8" s="4">
-        <v>0.262336193745653</v>
+        <v>0.2418883676950785</v>
       </c>
       <c r="K8" s="4">
         <v>84.44805194805184</v>
@@ -4811,13 +4811,13 @@
         <v>1.515151515151515</v>
       </c>
       <c r="H9" s="4">
-        <v>0.7645851448231811</v>
+        <v>0.7642807031002138</v>
       </c>
       <c r="I9" s="4">
-        <v>0.7869184263636957</v>
+        <v>0.7855788827826398</v>
       </c>
       <c r="J9" s="4">
-        <v>1.146657920072276</v>
+        <v>1.136321752024586</v>
       </c>
       <c r="K9" s="4">
         <v>75.61997526283245</v>
@@ -4861,13 +4861,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1306050294329321</v>
+        <v>0.1299307416502256</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1240591682967851</v>
+        <v>0.1238825691156</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1334754537067264</v>
+        <v>0.1337519733464222</v>
       </c>
       <c r="K10" s="4">
         <v>88.72088229231075</v>
@@ -4911,13 +4911,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.4224079482719772</v>
+        <v>0.4673957920954005</v>
       </c>
       <c r="I11" s="4">
-        <v>0.37979201942206</v>
+        <v>0.3559477009534928</v>
       </c>
       <c r="J11" s="4">
-        <v>0.3659610833482541</v>
+        <v>0.3585135131658287</v>
       </c>
       <c r="K11" s="4">
         <v>79.67274788703332</v>
@@ -4961,13 +4961,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2507933636119498</v>
+        <v>0.2478166220877047</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2379041564685132</v>
+        <v>0.2353308197866564</v>
       </c>
       <c r="J12" s="4">
-        <v>0.2368620613896876</v>
+        <v>0.2382972189354018</v>
       </c>
       <c r="K12" s="4">
         <v>83.62811791383217</v>
@@ -5011,13 +5011,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.18135187838891</v>
+        <v>0.1814161263374416</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1528517133772216</v>
+        <v>0.1507728290585724</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1742287755728625</v>
+        <v>0.1769457869099816</v>
       </c>
       <c r="K13" s="4">
         <v>85.29684601113155</v>
@@ -5061,13 +5061,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1042012711115625</v>
+        <v>0.103291939583284</v>
       </c>
       <c r="I14" s="4">
-        <v>0.08773965982243458</v>
+        <v>0.08740402607944017</v>
       </c>
       <c r="J14" s="4">
-        <v>0.09283138716668263</v>
+        <v>0.09014877743320994</v>
       </c>
       <c r="K14" s="4">
         <v>93.30653473510587</v>
@@ -5111,13 +5111,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1851713200789029</v>
+        <v>0.1842870578626825</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1769456126269308</v>
+        <v>0.1757760798631127</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1840920238811511</v>
+        <v>0.1815087912382043</v>
       </c>
       <c r="K15" s="4">
         <v>85.95598845598796</v>
@@ -5161,13 +5161,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1004888876670238</v>
+        <v>0.1013388774596461</v>
       </c>
       <c r="I16" s="4">
-        <v>0.08790512641497085</v>
+        <v>0.08514966162158588</v>
       </c>
       <c r="J16" s="4">
-        <v>0.08785127852395866</v>
+        <v>0.08827208724927464</v>
       </c>
       <c r="K16" s="4">
         <v>94.46660482374725</v>
@@ -5211,13 +5211,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.4693531977545475</v>
+        <v>0.4666080241871968</v>
       </c>
       <c r="I17" s="4">
-        <v>0.4521460871942597</v>
+        <v>0.4512800674264004</v>
       </c>
       <c r="J17" s="4">
-        <v>0.5270339532374112</v>
+        <v>0.5274241523483933</v>
       </c>
       <c r="K17" s="4">
         <v>82.74118738404395</v>
@@ -6914,16 +6914,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2365006847618542</v>
+        <v>0.2257669779223761</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3112217314695822</v>
+        <v>0.3103084135221394</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2704940401743303</v>
+        <v>0.2699753114275582</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -6973,13 +6973,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.182313069951443</v>
+        <v>0.175568381691896</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1861945056736452</v>
+        <v>0.1856324483186829</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1735726461436639</v>
@@ -7032,7 +7032,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2498152984301806</v>
+        <v>0.2271958951880109</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -7214,16 +7214,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.261748036732109</v>
+        <v>-0.2620787777929614</v>
       </c>
       <c r="O3" s="5">
         <v>19</v>
       </c>
       <c r="P3" s="4">
-        <v>0.454508610990181</v>
+        <v>0.4545637345003231</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4856732270521322</v>
+        <v>0.4856558196278767</v>
       </c>
       <c r="R3" s="5">
         <v>19</v>
@@ -7273,13 +7273,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1481754930891969</v>
+        <v>-0.1539970386620979</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4628533187687032</v>
+        <v>0.461397932375478</v>
       </c>
       <c r="Q4" s="4">
         <v>0.3879226356282419</v>
@@ -7512,16 +7512,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2824309715401676</v>
+        <v>0.2961258279757573</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3410802205226239</v>
+        <v>0.3414102763881283</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.294852504655004</v>
+        <v>0.2943678889764719</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -7571,16 +7571,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.178446861844663</v>
+        <v>0.2491246221229346</v>
       </c>
       <c r="O4" s="5">
         <v>23</v>
       </c>
       <c r="P4" s="4">
-        <v>0.235957452482749</v>
+        <v>0.2308274933508073</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2120746640573141</v>
+        <v>0.2036487171249283</v>
       </c>
       <c r="R4" s="5">
         <v>23</v>
@@ -7630,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.08336501773402698</v>
+        <v>0.08023246921978</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -7812,16 +7812,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1668170803688245</v>
+        <v>0.04950018431154035</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3664842893871482</v>
+        <v>0.4104422975390536</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4330698539663239</v>
+        <v>0.4252487275625049</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -7871,16 +7871,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.270213575956892</v>
+        <v>0.2425321163207173</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3169011667964461</v>
+        <v>0.312287590190417</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3114921601638262</v>
+        <v>0.3100352412356065</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -7930,16 +7930,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1283523900644553</v>
+        <v>0.1068964804394454</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1308784566327996</v>
+        <v>0.1237264867577963</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09083034417498766</v>
+        <v>0.08653916224998567</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.891114195748157</v>
+        <v>0.8963504340380837</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.8438621777351821</v>
+        <v>0.8598188444897303</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
@@ -8230,16 +8230,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.7954851719856819</v>
+        <v>0.8195425375781369</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07257860401909492</v>
+        <v>0.06891940885416403</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07257860401909492</v>
+        <v>0.06891940885416403</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
